--- a/output/pdf_financials_xlsx/NAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/NAQ.P.xlsx
@@ -3391,19 +3391,19 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.1538</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.1538</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.1272</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.1272</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>0.1272</v>
       </c>
       <c r="G92" s="3" t="n">
         <v>0</v>
@@ -5870,7 +5870,11 @@
           <t>Reserves 4</t>
         </is>
       </c>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E21" t="inlineStr">
         <is>
           <t>-</t>
@@ -6090,7 +6094,11 @@
           <t>Reserves 3</t>
         </is>
       </c>
-      <c r="D25" t="inlineStr"/>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E25" t="inlineStr">
         <is>
           <t>-</t>
@@ -6648,7 +6656,11 @@
           <t>Reserves 3</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -7036,7 +7048,11 @@
           <t>Reserves 5</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E42" s="5" t="n">
         <v>0.1538</v>
       </c>

--- a/output/pdf_financials_xlsx/NAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/NAQ.P.xlsx
@@ -1513,28 +1513,28 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.8982599999999999</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.473493</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.313205</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.092723</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.059099</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.016843</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.02585</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.006056</v>
       </c>
     </row>
     <row r="35">
@@ -1575,28 +1575,28 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.8982599999999999</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.473493</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.313205</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.092723</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.059099</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.016843</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.02585</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.006056</v>
       </c>
     </row>
     <row r="37">
@@ -1947,16 +1947,16 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.8982599999999999</v>
+        <v>0</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.475383</v>
+        <v>0.00189</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.314262</v>
+        <v>0.001057</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.099773</v>
+        <v>0.00705</v>
       </c>
       <c r="F48" s="3" t="n">
         <v>0</v>
@@ -4930,7 +4930,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" s="5" t="n">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>InterestExpense</t>
+          <t>InterestExpenseOperating</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
